--- a/data/use_cases/uc12_part_time_new_contract_result.xlsx
+++ b/data/use_cases/uc12_part_time_new_contract_result.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="5">
@@ -12113,7 +12113,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Дата построения 04.07.2026</t>
+          <t>Дата построения 10.07.2026</t>
         </is>
       </c>
     </row>
